--- a/python/excel-to-testlink/input/testcase_template2.xlsx
+++ b/python/excel-to-testlink/input/testcase_template2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2087\Desktop\REPO\daily-code-filing\python\excel-to-testlink\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695D4752-83D1-47CA-BE74-36FAC496A916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CAE81DA-EF6B-4C6F-BF52-900A85B30FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="348" windowWidth="30936" windowHeight="17040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="89">
   <si>
     <t>界面要素检查</t>
   </si>
@@ -292,18 +292,34 @@
   </si>
   <si>
     <t>suite_path</t>
+  </si>
+  <si>
+    <t>auther</t>
+  </si>
+  <si>
+    <t>pwz</t>
+  </si>
+  <si>
+    <t>jhc</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -370,24 +386,30 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -691,7 +713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="23.6640625" customWidth="1"/>
@@ -702,9 +724,10 @@
     <col min="6" max="6" width="47.109375" customWidth="1"/>
     <col min="7" max="7" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="20.25" customHeight="1">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="20.25" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>85</v>
       </c>
@@ -729,8 +752,11 @@
       <c r="H1" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="28.8">
+      <c r="I1" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="28.8">
       <c r="A2" s="5" t="s">
         <v>48</v>
       </c>
@@ -755,8 +781,11 @@
       <c r="H2" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="43.2">
+      <c r="I2" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="28.8">
       <c r="A3" s="5" t="s">
         <v>48</v>
       </c>
@@ -781,8 +810,11 @@
       <c r="H3" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="28.8">
+      <c r="I3" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="28.8">
       <c r="A4" s="5" t="s">
         <v>48</v>
       </c>
@@ -807,8 +839,11 @@
       <c r="H4" s="5" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="28.8">
+      <c r="I4" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="28.8">
       <c r="A5" s="5" t="s">
         <v>48</v>
       </c>
@@ -833,8 +868,11 @@
       <c r="H5" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="28.8">
+      <c r="I5" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="28.8">
       <c r="A6" s="5" t="s">
         <v>48</v>
       </c>
@@ -859,8 +897,11 @@
       <c r="H6" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="28.8">
+      <c r="I6" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="28.8">
       <c r="A7" s="5" t="s">
         <v>48</v>
       </c>
@@ -885,8 +926,11 @@
       <c r="H7" s="5" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="43.2">
+      <c r="I7" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="28.8">
       <c r="A8" s="5" t="s">
         <v>48</v>
       </c>
@@ -911,8 +955,11 @@
       <c r="H8" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="5" t="s">
         <v>48</v>
       </c>
@@ -937,8 +984,11 @@
       <c r="H9" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="5" t="s">
         <v>48</v>
       </c>
@@ -963,8 +1013,11 @@
       <c r="H10" s="5" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="5" t="s">
         <v>48</v>
       </c>
@@ -989,8 +1042,11 @@
       <c r="H11" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="5" t="s">
         <v>49</v>
       </c>
@@ -1015,8 +1071,11 @@
       <c r="H12" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="5" t="s">
         <v>49</v>
       </c>
@@ -1041,8 +1100,11 @@
       <c r="H13" s="5" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="5" t="s">
         <v>49</v>
       </c>
@@ -1067,8 +1129,11 @@
       <c r="H14" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="I14" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="5" t="s">
         <v>49</v>
       </c>
@@ -1093,8 +1158,11 @@
       <c r="H15" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="I15" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="5" t="s">
         <v>49</v>
       </c>
@@ -1119,9 +1187,12 @@
       <c r="H16" s="5" t="s">
         <v>84</v>
       </c>
+      <c r="I16" s="6" t="s">
+        <v>88</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/python/excel-to-testlink/input/testcase_template2.xlsx
+++ b/python/excel-to-testlink/input/testcase_template2.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2087\Desktop\REPO\daily-code-filing\python\excel-to-testlink\input\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CAE81DA-EF6B-4C6F-BF52-900A85B30FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="348" windowWidth="30936" windowHeight="17040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12690"/>
   </bookViews>
   <sheets>
     <sheet name="suitename1" sheetId="13" r:id="rId1"/>
@@ -23,9 +17,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+  <si>
+    <t>suite_path</t>
+  </si>
+  <si>
+    <t>casename</t>
+  </si>
+  <si>
+    <t>summary</t>
+  </si>
+  <si>
+    <t>precondition</t>
+  </si>
+  <si>
+    <t>step</t>
+  </si>
+  <si>
+    <t>excepted</t>
+  </si>
+  <si>
+    <t>execution_type</t>
+  </si>
+  <si>
+    <t>priority</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t>手续费核算</t>
+  </si>
   <si>
     <t>界面要素检查</t>
+  </si>
+  <si>
+    <t>test-summary-1</t>
+  </si>
+  <si>
+    <t>test-precondition-1</t>
   </si>
   <si>
     <t>1.打开手续费核算界面，检查界面要素
@@ -36,7 +66,25 @@
 2.界面要素与需求文档一致</t>
   </si>
   <si>
+    <t>manual</t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>pwz</t>
+  </si>
+  <si>
+    <t>手续费核算/查询</t>
+  </si>
+  <si>
     <t>按默认条件查询</t>
+  </si>
+  <si>
+    <t>test-summary-2</t>
+  </si>
+  <si>
+    <t>test-precondition-2</t>
   </si>
   <si>
     <t>1.输入任意查询条件，点击查询
@@ -47,18 +95,42 @@
 2.数据更新成功，符合默认条件</t>
   </si>
   <si>
+    <t>automated</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>按银行客户号查询</t>
+  </si>
+  <si>
+    <t>test-summary-3</t>
+  </si>
+  <si>
+    <t>test-precondition-3</t>
+  </si>
+  <si>
+    <t>1.打开手续费核算界面
+2.输入特定银行客户号，点击查询</t>
+  </si>
+  <si>
     <t>1.正确打开
 2.查询成功，数据正确</t>
   </si>
   <si>
-    <t>按银行客户号查询</t>
-  </si>
-  <si>
-    <t>1.打开手续费核算界面
-2.输入特定银行客户号，点击查询</t>
+    <t>low</t>
+  </si>
+  <si>
+    <t>手续费核算/查询/子查询A</t>
   </si>
   <si>
     <t>按保证金户口号查询</t>
+  </si>
+  <si>
+    <t>test-summary-4</t>
+  </si>
+  <si>
+    <t>test-precondition-4</t>
   </si>
   <si>
     <t>1.打开手续费核算界面
@@ -68,6 +140,12 @@
     <t>按客户中文名称查询</t>
   </si>
   <si>
+    <t>test-summary-5</t>
+  </si>
+  <si>
+    <t>test-precondition-5</t>
+  </si>
+  <si>
     <t>1.打开手续费核算界面
 2.输入特定客户中文名称，点击查询</t>
   </si>
@@ -75,11 +153,26 @@
     <t>按清算客户号查询</t>
   </si>
   <si>
+    <t>test-summary-6</t>
+  </si>
+  <si>
+    <t>test-precondition-6</t>
+  </si>
+  <si>
     <t>1.打开手续费核算界面
 2.输入特定清算客户号，点击查询</t>
   </si>
   <si>
+    <t>手续费核算/查询/子查询B</t>
+  </si>
+  <si>
     <t>按综合条件查询</t>
+  </si>
+  <si>
+    <t>test-summary-7</t>
+  </si>
+  <si>
+    <t>test-precondition-7</t>
   </si>
   <si>
     <t>1.打开手续费核算界面
@@ -90,9 +183,18 @@
 2.对于每组特定的条件，查询结果均正确</t>
   </si>
   <si>
+    <t>jhc</t>
+  </si>
+  <si>
     <t>模糊查询功能校验</t>
   </si>
   <si>
+    <t>test-summary-8</t>
+  </si>
+  <si>
+    <t>test-precondition-8</t>
+  </si>
+  <si>
     <t>1.按照需求文档描述，对所有支持模糊查询的字段依次进行模糊查询，校验模糊查询是否正常可用，结果是否正确</t>
   </si>
   <si>
@@ -102,6 +204,12 @@
     <t>非法输入拦截校验</t>
   </si>
   <si>
+    <t>test-summary-9</t>
+  </si>
+  <si>
+    <t>test-precondition-9</t>
+  </si>
+  <si>
     <t>1.按照需求文档描述，对字段进行非法输入，点击查询</t>
   </si>
   <si>
@@ -111,15 +219,30 @@
     <t>查询结果排序校验</t>
   </si>
   <si>
+    <t>test-summary-10</t>
+  </si>
+  <si>
+    <t>test-precondition-10</t>
+  </si>
+  <si>
     <t>1.检查查询结果排序情况</t>
   </si>
   <si>
     <t>1.按照交易编码升序排序</t>
   </si>
   <si>
+    <t>手续费核算/数据校验</t>
+  </si>
+  <si>
     <t>DE17数据读取正确</t>
   </si>
   <si>
+    <t>test-summary-11</t>
+  </si>
+  <si>
+    <t>test-precondition-11</t>
+  </si>
+  <si>
     <t>1.检查计费区间、计费日、支付日、应缴手续费（应缴给上清所）这四个字段的值是否正确</t>
   </si>
   <si>
@@ -129,6 +252,12 @@
     <t>手续费上浮部分总额计算正确</t>
   </si>
   <si>
+    <t>test-summary-12</t>
+  </si>
+  <si>
+    <t>test-precondition-12</t>
+  </si>
+  <si>
     <t>1.根据每日DE18导入情况，计算应缴手续费总额，与界面显示的金额进行对比</t>
   </si>
   <si>
@@ -138,6 +267,12 @@
     <t>应缴手续费金额正确</t>
   </si>
   <si>
+    <t>test-summary-13</t>
+  </si>
+  <si>
+    <t>test-precondition-13</t>
+  </si>
+  <si>
     <t>1.检查应缴手续费金额是否与DE17文件中一致</t>
   </si>
   <si>
@@ -147,6 +282,12 @@
     <t>季度内费率有变化，上浮计算正确</t>
   </si>
   <si>
+    <t>test-summary-14</t>
+  </si>
+  <si>
+    <t>test-precondition-14</t>
+  </si>
+  <si>
     <t>1.季度内费率乘数有变化，检查最后的上浮总额计算是否正确</t>
   </si>
   <si>
@@ -156,177 +297,31 @@
     <t>费率为0，上浮计算正确</t>
   </si>
   <si>
+    <t>test-summary-15</t>
+  </si>
+  <si>
+    <t>test-precondition-15</t>
+  </si>
+  <si>
     <t>1.对某一客户设置其所有手续费率乘数为0，检查其上浮总额计算是否正确</t>
-  </si>
-  <si>
-    <t>precondition</t>
-  </si>
-  <si>
-    <t>step</t>
-  </si>
-  <si>
-    <t>excepted</t>
-  </si>
-  <si>
-    <t>execution_type</t>
-  </si>
-  <si>
-    <t>priority</t>
-  </si>
-  <si>
-    <t>summary</t>
-  </si>
-  <si>
-    <t>casename</t>
-  </si>
-  <si>
-    <t>手续费核算/查询</t>
-  </si>
-  <si>
-    <t>手续费核算/数据校验</t>
-  </si>
-  <si>
-    <t>test-precondition-1</t>
-  </si>
-  <si>
-    <t>test-precondition-2</t>
-  </si>
-  <si>
-    <t>test-precondition-3</t>
-  </si>
-  <si>
-    <t>test-precondition-4</t>
-  </si>
-  <si>
-    <t>test-precondition-5</t>
-  </si>
-  <si>
-    <t>test-precondition-6</t>
-  </si>
-  <si>
-    <t>test-precondition-7</t>
-  </si>
-  <si>
-    <t>test-precondition-8</t>
-  </si>
-  <si>
-    <t>test-precondition-9</t>
-  </si>
-  <si>
-    <t>test-precondition-10</t>
-  </si>
-  <si>
-    <t>test-precondition-11</t>
-  </si>
-  <si>
-    <t>test-precondition-12</t>
-  </si>
-  <si>
-    <t>test-precondition-13</t>
-  </si>
-  <si>
-    <t>test-precondition-14</t>
-  </si>
-  <si>
-    <t>test-precondition-15</t>
-  </si>
-  <si>
-    <t>test-summary-1</t>
-  </si>
-  <si>
-    <t>test-summary-2</t>
-  </si>
-  <si>
-    <t>test-summary-3</t>
-  </si>
-  <si>
-    <t>test-summary-4</t>
-  </si>
-  <si>
-    <t>test-summary-5</t>
-  </si>
-  <si>
-    <t>test-summary-6</t>
-  </si>
-  <si>
-    <t>test-summary-7</t>
-  </si>
-  <si>
-    <t>test-summary-8</t>
-  </si>
-  <si>
-    <t>test-summary-9</t>
-  </si>
-  <si>
-    <t>test-summary-10</t>
-  </si>
-  <si>
-    <t>test-summary-11</t>
-  </si>
-  <si>
-    <t>test-summary-12</t>
-  </si>
-  <si>
-    <t>test-summary-13</t>
-  </si>
-  <si>
-    <t>test-summary-14</t>
-  </si>
-  <si>
-    <t>test-summary-15</t>
-  </si>
-  <si>
-    <t>automated</t>
-  </si>
-  <si>
-    <t>manual</t>
-  </si>
-  <si>
-    <t>high</t>
-  </si>
-  <si>
-    <t>medium</t>
-  </si>
-  <si>
-    <t>low</t>
-  </si>
-  <si>
-    <t>suite_path</t>
-  </si>
-  <si>
-    <t>auther</t>
-  </si>
-  <si>
-    <t>pwz</t>
-  </si>
-  <si>
-    <t>jhc</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -343,21 +338,352 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -380,9 +706,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -390,39 +958,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -707,493 +1319,493 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="23.6640625" customWidth="1"/>
-    <col min="2" max="2" width="32.33203125" customWidth="1"/>
-    <col min="3" max="3" width="24.21875" customWidth="1"/>
-    <col min="4" max="4" width="23.5546875" customWidth="1"/>
-    <col min="5" max="5" width="44.21875" customWidth="1"/>
-    <col min="6" max="6" width="47.109375" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9" style="7"/>
+    <col min="1" max="1" width="24.625" customWidth="1"/>
+    <col min="2" max="2" width="32.3333333333333" customWidth="1"/>
+    <col min="3" max="3" width="24.2166666666667" customWidth="1"/>
+    <col min="4" max="4" width="23.5583333333333" customWidth="1"/>
+    <col min="5" max="5" width="44.2166666666667" customWidth="1"/>
+    <col min="6" max="6" width="47.1083333333333" customWidth="1"/>
+    <col min="7" max="7" width="16.6666666666667" customWidth="1"/>
+    <col min="8" max="8" width="9.88333333333333" customWidth="1"/>
+    <col min="9" max="9" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:9">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" ht="27" spans="1:9">
+      <c r="A2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" ht="27" spans="1:9">
+      <c r="A3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="27" spans="1:9">
+      <c r="A4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="27" spans="1:9">
+      <c r="A5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="27" spans="1:9">
+      <c r="A6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="27" spans="1:9">
+      <c r="A7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="27" spans="1:9">
+      <c r="A8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="28.8">
-      <c r="A2" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="E8" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="28.8">
-      <c r="A3" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="G8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="28.8">
-      <c r="A4" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="28.8">
-      <c r="A5" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="28.8">
-      <c r="A6" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="28.8">
-      <c r="A7" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="28.8">
-      <c r="A8" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>88</v>
+        <v>25</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>88</v>
+        <v>31</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>80</v>
-      </c>
       <c r="H11" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>88</v>
+        <v>16</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="5" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="F12" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>88</v>
+        <v>25</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="5" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="C13" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F13" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>88</v>
+      <c r="I13" s="7" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="5" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="F14" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>88</v>
+        <v>16</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="5" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="E15" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="F15" t="s">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>88</v>
+        <v>25</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="5" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="F16" t="s">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>88</v>
+        <v>31</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>